--- a/assets/template.xlsx
+++ b/assets/template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ak\fbm-standards\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andrew.Kim\gkd\forks\fbm-excel-skill\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CCE9C3E3-352E-480E-9E01-CAC49D1A16B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{53F67660-8192-435B-9877-5EFD94DB68B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="46296" windowHeight="25416" xr2:uid="{E7042311-6741-4388-871D-F9908931CBC2}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="34560" windowHeight="18648" xr2:uid="{6CCD779C-F5E7-4672-8593-8D78333E2E07}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
@@ -21,13 +21,20 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Inputs!$B$5:$F$5</definedName>
+    <definedName name="AsOfDate">Cover!$C$14</definedName>
     <definedName name="Discount_Rate">Reference!$C$6</definedName>
+    <definedName name="FY_End">Reference!$C$11</definedName>
+    <definedName name="FY_Start">Reference!$C$10</definedName>
     <definedName name="Growth_Rate">Inputs!$C$7:$F$7</definedName>
+    <definedName name="Inflation_Rate">Reference!$C$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">Calc!$5:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">Inputs!$5:$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">Output!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">Output!$8:$8</definedName>
+    <definedName name="ReportingCurrency">Cover!$C$16</definedName>
     <definedName name="Revenue_Input">Inputs!$C$6:$F$6</definedName>
+    <definedName name="Scale">Cover!$C$15</definedName>
     <definedName name="Tax_Rate">Reference!$C$7</definedName>
+    <definedName name="WACC">Reference!$C$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -53,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="94">
   <si>
     <t>FBM Excel Formatting Standard</t>
   </si>
@@ -64,10 +71,34 @@
     <t>Prepared by:</t>
   </si>
   <si>
+    <t>Andrew Kim</t>
+  </si>
+  <si>
     <t>Department:</t>
   </si>
   <si>
-    <t>Date:</t>
+    <t>Operations FP&amp;A</t>
+  </si>
+  <si>
+    <t>As-of date:</t>
+  </si>
+  <si>
+    <t>Reporting scale:</t>
+  </si>
+  <si>
+    <t>$ thousands</t>
+  </si>
+  <si>
+    <t>Reporting currency:</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>Contact:</t>
+  </si>
+  <si>
+    <t>andrew.kim@fbm.com</t>
   </si>
   <si>
     <t>Version:</t>
@@ -79,16 +110,58 @@
     <t>Purpose:</t>
   </si>
   <si>
-    <t>Andrew Kim</t>
-  </si>
-  <si>
-    <t>Operations FP&amp;A</t>
-  </si>
-  <si>
-    <t>Standard FBM workbook template with cell styles, named ranges, and example sheets.</t>
-  </si>
-  <si>
-    <t>Legend</t>
+    <t>Working template with cell styles, named ranges, example sheets</t>
+  </si>
+  <si>
+    <t>Table of Contents</t>
+  </si>
+  <si>
+    <t>Data Sources</t>
+  </si>
+  <si>
+    <t>Source system</t>
+  </si>
+  <si>
+    <t>Last refreshed</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>[e.g. SAP S/4HANA]</t>
+  </si>
+  <si>
+    <t>[YYYY-MM-DD]</t>
+  </si>
+  <si>
+    <t>[name]</t>
+  </si>
+  <si>
+    <t>[notes]</t>
+  </si>
+  <si>
+    <t>Version History</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Author</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>Initial release of v1.2 template (PR-A foundation + PR-B output polish).</t>
+  </si>
+  <si>
+    <t>Cell Style Legend</t>
   </si>
   <si>
     <t>Cell Style</t>
@@ -169,9 +242,15 @@
     <t>Reference</t>
   </si>
   <si>
+    <t>FBM Confidential â€” Do Not Distribute</t>
+  </si>
+  <si>
     <t>Blue text cells are user-editable. Do not overwrite black formula cells.</t>
   </si>
   <si>
+    <t>$ thousands (USD)</t>
+  </si>
+  <si>
     <t>Item</t>
   </si>
   <si>
@@ -220,6 +299,15 @@
     <t>Output Summary</t>
   </si>
   <si>
+    <t>FY2029 Revenue</t>
+  </si>
+  <si>
+    <t>FY2029 Gross Profit</t>
+  </si>
+  <si>
+    <t>FY2029 Gross Margin</t>
+  </si>
+  <si>
     <t>KPI</t>
   </si>
   <si>
@@ -241,7 +329,16 @@
     <t>Tax rate</t>
   </si>
   <si>
+    <t>WACC</t>
+  </si>
+  <si>
+    <t>Inflation rate</t>
+  </si>
+  <si>
     <t>FY start month</t>
+  </si>
+  <si>
+    <t>FY end month</t>
   </si>
   <si>
     <t>Working days/yr</t>
@@ -251,13 +348,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="10">
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.0%;\(0.0%\);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
+    <numFmt numFmtId="166" formatCode="\+#,##0;\(#,##0\);&quot;-&quot;"/>
+    <numFmt numFmtId="167" formatCode="\+&quot;$&quot;#,##0;\(&quot;$&quot;#,##0\);&quot;-&quot;"/>
+    <numFmt numFmtId="168" formatCode="\+0.0%;\(0.0%\);&quot;-&quot;"/>
+    <numFmt numFmtId="169" formatCode="\+0&quot; bps&quot;;\(0\)&quot; bps&quot;;&quot;-&quot;"/>
+    <numFmt numFmtId="170" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="171" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -304,15 +407,15 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -345,6 +448,20 @@
       <family val="2"/>
     </font>
     <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF636466"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color rgb="FF093254"/>
+      <name val="Rockwell"/>
+      <family val="1"/>
+    </font>
+    <font>
       <b/>
       <sz val="20"/>
       <color rgb="FF093254"/>
@@ -354,6 +471,21 @@
     <font>
       <sz val="14"/>
       <color rgb="FF636466"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
+      <color rgb="FF008000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -374,7 +506,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -396,6 +528,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE7E6E6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7F7F7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -453,7 +591,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="16">
+  <cellStyleXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="2" fillId="0" borderId="0"/>
@@ -464,7 +602,7 @@
     <xf numFmtId="41" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1">
@@ -476,13 +614,31 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="12"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="12" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="12" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="14" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="11" applyBorder="1">
@@ -491,50 +647,107 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="11" applyBorder="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="10">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="25" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="10">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="0" xfId="4"/>
     <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="7"/>
     <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="8"/>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="9" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="10" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="16">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="17">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="10" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="2" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="3"/>
     <xf numFmtId="42" fontId="4" fillId="0" borderId="0" xfId="7" applyNumberFormat="1"/>
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0" xfId="5"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" xfId="23" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="24">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="14" fillId="0" borderId="0" xfId="23" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="7" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="42" fontId="12" fillId="0" borderId="0" xfId="13" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="16">
-    <cellStyle name="FBM Assumption" xfId="9" xr:uid="{96C0EE95-5D79-470A-A736-06E41E8EBA06}"/>
-    <cellStyle name="FBM Date" xfId="14" xr:uid="{86DF2E66-800A-4CB8-A746-8FD091E01773}"/>
-    <cellStyle name="FBM External" xfId="8" xr:uid="{BB651C1B-C3A8-4421-84D7-C36E352C4280}"/>
-    <cellStyle name="FBM Formula" xfId="4" xr:uid="{6865716C-3D78-4606-B6AF-60C25DB1B753}"/>
-    <cellStyle name="FBM Formula $" xfId="5" xr:uid="{F1B63EAA-BF2E-4A31-805B-F3BEA1E008D4}"/>
-    <cellStyle name="FBM Formula %" xfId="6" xr:uid="{88F462EA-45D9-4C7C-9776-B12F55708821}"/>
-    <cellStyle name="FBM Header" xfId="10" xr:uid="{2B39E0B0-02F6-49DD-BBC5-908374B9444F}"/>
-    <cellStyle name="FBM Input" xfId="1" xr:uid="{AC8EB86F-5856-4D7F-8BE8-DE17A89F9AE9}"/>
-    <cellStyle name="FBM Input $" xfId="2" xr:uid="{48277B8E-98B0-4B81-8A78-D1A1BA6359F1}"/>
-    <cellStyle name="FBM Input %" xfId="3" xr:uid="{04F86235-49DF-4C06-8F27-1A6E770FBE07}"/>
-    <cellStyle name="FBM Link" xfId="7" xr:uid="{47B3A732-7CC6-4938-92FC-5D37D9B8B3E1}"/>
-    <cellStyle name="FBM Subheader" xfId="11" xr:uid="{85DA115A-7BD4-4BFD-8D41-E70432FD9E00}"/>
-    <cellStyle name="FBM Title" xfId="12" xr:uid="{74C57A3B-176F-4A45-9518-9E03227B0671}"/>
-    <cellStyle name="FBM Total" xfId="13" xr:uid="{B9D1CC19-ECF3-49F7-BFE3-18DEF5ED4E6C}"/>
-    <cellStyle name="FBM Year" xfId="15" xr:uid="{635E5135-FB9D-4C7E-BDE4-784FC5E3D9F6}"/>
+  <cellStyles count="26">
+    <cellStyle name="FBM Assumption" xfId="9" xr:uid="{E880336C-8A72-4A94-9EE2-CA633939DF53}"/>
+    <cellStyle name="FBM Band" xfId="22" xr:uid="{40FB81D0-82AA-4F50-AD09-DAAC26BC2221}"/>
+    <cellStyle name="FBM Date" xfId="14" xr:uid="{C7DA40D7-CB67-42E8-B66F-0F46452C7708}"/>
+    <cellStyle name="FBM External" xfId="8" xr:uid="{450CA289-8CA1-4486-89AD-B8A31E8F6E9D}"/>
+    <cellStyle name="FBM Formula" xfId="4" xr:uid="{DBDA0E8A-F60B-4811-A3DB-B1A4E44A2010}"/>
+    <cellStyle name="FBM Formula $" xfId="5" xr:uid="{52F61E3A-3BC7-4697-9E4F-A534AAB5FFB7}"/>
+    <cellStyle name="FBM Formula %" xfId="6" xr:uid="{B5BC99A7-B76B-432B-B305-E8B24096F4A2}"/>
+    <cellStyle name="FBM Header" xfId="10" xr:uid="{5C4EFE83-9D00-4259-8FAE-CA4FB68DB63E}"/>
+    <cellStyle name="FBM Input" xfId="1" xr:uid="{1E82695E-0C83-4964-9B6D-0F65939C2C20}"/>
+    <cellStyle name="FBM Input $" xfId="2" xr:uid="{E84246DF-2131-4296-B361-C5877FA1139B}"/>
+    <cellStyle name="FBM Input %" xfId="3" xr:uid="{59F69B06-378E-4E65-8829-EE1D08825540}"/>
+    <cellStyle name="FBM KPI Big" xfId="23" xr:uid="{9D03FCD5-8812-4371-A6F7-F7E45E0BEDB6}"/>
+    <cellStyle name="FBM KPI Label" xfId="24" xr:uid="{ED06428F-4F6C-43EA-87B9-80B43858C633}"/>
+    <cellStyle name="FBM Link" xfId="7" xr:uid="{53907B19-7A04-4E6D-B94E-AAA4E0E2FB91}"/>
+    <cellStyle name="FBM Subheader" xfId="11" xr:uid="{EF0ED9C6-2A71-42FA-AFAC-F9A1CCE984CE}"/>
+    <cellStyle name="FBM Subtitle" xfId="16" xr:uid="{314024F5-DDE1-4D84-93C5-6671338E3DA3}"/>
+    <cellStyle name="FBM Title" xfId="12" xr:uid="{41D624D5-74C0-4EEA-B984-5E51DE1BF0E2}"/>
+    <cellStyle name="FBM Total" xfId="13" xr:uid="{79434CE1-C74C-45C4-8AA8-F9EEFF29D548}"/>
+    <cellStyle name="FBM Units" xfId="17" xr:uid="{0FD30B3E-87B3-4880-88E3-A42586797FF0}"/>
+    <cellStyle name="FBM Variance" xfId="18" xr:uid="{FB8F8110-8555-411A-9D71-BD7D2E3282F6}"/>
+    <cellStyle name="FBM Variance $" xfId="19" xr:uid="{DF6F6B63-DECE-485B-8E11-24C2E1FF05B9}"/>
+    <cellStyle name="FBM Variance %" xfId="20" xr:uid="{7A4DB95D-1FA1-4E7B-99C0-A3B785A74493}"/>
+    <cellStyle name="FBM Variance bps" xfId="21" xr:uid="{250F2E4D-62A7-4A8C-BED4-BA433E54B239}"/>
+    <cellStyle name="FBM Year" xfId="15" xr:uid="{1A127C03-C751-4FA9-8ADF-2CA3CD77E670}"/>
+    <cellStyle name="Hyperlink" xfId="25" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF7F7F7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF7F7F7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF7F7F7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF7F7F7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -557,8 +770,8 @@
       <xdr:rowOff>71120</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>360680</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>414020</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>116840</xdr:rowOff>
     </xdr:to>
@@ -567,7 +780,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F42E07D7-4D47-EB14-7025-F74FD4546820}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{578CF97D-4E5E-4A70-C671-1D3E9B726ED2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -918,219 +1131,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9891BDCA-C08B-4CF9-A0CC-FE0EE0AC2032}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6C29372-47A8-498F-B0ED-4D9B3B76F385}">
   <sheetPr>
     <tabColor rgb="FF093254"/>
   </sheetPr>
-  <dimension ref="B8:D32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="5.77734375" customWidth="1"/>
-    <col min="2" max="10" width="15.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="8" spans="2:3" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="B8" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="B10" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B12" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B13" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B14" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" s="6">
-        <v>46163</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B15" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B16" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="5"/>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B17" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B20" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B21" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B22" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="5">
-        <v>1000</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B23" t="s">
-        <v>17</v>
-      </c>
-      <c r="C23" s="11">
-        <v>2000</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B24" t="s">
-        <v>19</v>
-      </c>
-      <c r="C24" s="12">
-        <v>3000</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B25" t="s">
-        <v>21</v>
-      </c>
-      <c r="C25" s="13">
-        <v>4000</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B26" t="s">
-        <v>23</v>
-      </c>
-      <c r="C26" s="14">
-        <v>0.1</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B28" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B29" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B30" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C30" t="s">
-        <v>30</v>
-      </c>
-      <c r="D30" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B31" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C31" t="s">
-        <v>33</v>
-      </c>
-      <c r="D31" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B32" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C32" t="s">
-        <v>36</v>
-      </c>
-      <c r="D32" t="s">
-        <v>37</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B28:D28"/>
-  </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-  <headerFooter>
-    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;14FBM Excel Formatting Standard</oddHeader>
-    <oddFooter>&amp;R&amp;P of &amp;N&amp;L&amp;F</oddFooter>
-  </headerFooter>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4A7E1B6-B6AC-46DF-9244-4A0D22141E59}">
-  <sheetPr>
-    <tabColor rgb="FF1F4E79"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="B2:F9"/>
+  <dimension ref="B8:E56"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.77734375" customWidth="1"/>
@@ -1138,118 +1143,347 @@
     <col min="3" max="10" width="15.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="18" x14ac:dyDescent="0.35">
-      <c r="B2" s="1" t="s">
+    <row r="8" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B8" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B10" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B12" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B13" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B14" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="6">
+        <v>46171</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B16" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B17" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="5">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="5"/>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B23" s="9" t="str">
+        <f>HYPERLINK("#'Inputs'!A1","Inputs")</f>
+        <v>Inputs</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B24" s="9" t="str">
+        <f>HYPERLINK("#'Calc'!A1","Calc")</f>
+        <v>Calc</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B25" s="9" t="str">
+        <f>HYPERLINK("#'Output'!A1","Output")</f>
+        <v>Output</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B26" s="9" t="str">
+        <f>HYPERLINK("#'Reference'!A1","Reference")</f>
+        <v>Reference</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B29" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B30" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B31" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B35" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B36" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E36" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B3" s="18" t="s">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B37" s="11">
+        <v>1.2</v>
+      </c>
+      <c r="C37" s="12">
+        <v>46171</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B42" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B43" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B44" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="5">
+        <v>1000</v>
+      </c>
+      <c r="D44" s="11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="9" t="s">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B45" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C45" s="13">
+        <v>2000</v>
+      </c>
+      <c r="D45" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="19" t="s">
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B46" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="C46" s="14">
+        <v>3000</v>
+      </c>
+      <c r="D46" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="19" t="s">
+    </row>
+    <row r="47" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B47" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B6" s="10" t="s">
+      <c r="C47" s="15">
+        <v>4000</v>
+      </c>
+      <c r="D47" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="20">
-        <v>10000000</v>
-      </c>
-      <c r="D6" s="20">
-        <v>10500000</v>
-      </c>
-      <c r="E6" s="20">
-        <v>11025000</v>
-      </c>
-      <c r="F6" s="20">
-        <v>11576250</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B7" s="10" t="s">
+    </row>
+    <row r="48" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B48" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="21">
-        <v>0.05</v>
-      </c>
-      <c r="D7" s="21">
-        <v>0.05</v>
-      </c>
-      <c r="E7" s="21">
-        <v>0.05</v>
-      </c>
-      <c r="F7" s="21">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B8" s="10" t="s">
+      <c r="C48" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="D48" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="20">
-        <v>6000000</v>
-      </c>
-      <c r="D8" s="20">
-        <v>6300000</v>
-      </c>
-      <c r="E8" s="20">
-        <v>6615000</v>
-      </c>
-      <c r="F8" s="20">
-        <v>6945750</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B9" s="10" t="s">
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B50" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C50" s="8"/>
+      <c r="D50" s="8"/>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B51" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D51" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="5">
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B52" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C52" t="s">
         <v>52</v>
       </c>
-      <c r="E9" s="5">
+      <c r="D52" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B53" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C53" t="s">
         <v>55</v>
       </c>
-      <c r="F9" s="5">
+      <c r="D53" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B54" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C54" t="s">
         <v>58</v>
       </c>
+      <c r="D54" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B56" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C56" s="21"/>
+      <c r="D56" s="21"/>
+      <c r="E56" s="21"/>
     </row>
   </sheetData>
-  <autoFilter ref="B5:F5" xr:uid="{F4A7E1B6-B6AC-46DF-9244-4A0D22141E59}"/>
-  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <mergeCells count="6">
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B56:E56"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;12Inputs&amp;L&amp;G</oddHeader>
-    <oddFooter>&amp;R&amp;P of &amp;N&amp;L&amp;F&amp;C&amp;D</oddFooter>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;14FBM Excel Formatting Standard</oddHeader>
+    <oddFooter>&amp;L&amp;F&amp;C&amp;D  ·  v1.2  ·  As of 05/29/2026&amp;R&amp;P of &amp;N</oddFooter>
   </headerFooter>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C894B16E-F0B7-4A0B-988A-3691CE5C5286}">
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21A502A3-9C52-4270-99C9-763E766B38B8}">
   <sheetPr>
+    <tabColor rgb="FF1F4E79"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:F9"/>
+  <dimension ref="B2:F25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.77734375" customWidth="1"/>
@@ -1257,113 +1491,291 @@
     <col min="3" max="10" width="15.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B6" s="10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="22" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+    </row>
+    <row r="5" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="25">
+        <v>10000000</v>
+      </c>
+      <c r="D6" s="25">
+        <v>10500000</v>
+      </c>
+      <c r="E6" s="25">
+        <v>11025000</v>
+      </c>
+      <c r="F6" s="25">
+        <v>11576250</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="26">
+        <v>0.05</v>
+      </c>
+      <c r="D7" s="26">
+        <v>0.05</v>
+      </c>
+      <c r="E7" s="26">
+        <v>0.05</v>
+      </c>
+      <c r="F7" s="26">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="25">
+        <v>6000000</v>
+      </c>
+      <c r="D8" s="25">
+        <v>6300000</v>
+      </c>
+      <c r="E8" s="25">
+        <v>6615000</v>
+      </c>
+      <c r="F8" s="25">
+        <v>6945750</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="5">
         <v>50</v>
       </c>
-      <c r="C6" s="22">
+      <c r="D9" s="5">
+        <v>52</v>
+      </c>
+      <c r="E9" s="5">
+        <v>55</v>
+      </c>
+      <c r="F9" s="5">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="18" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="19" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+  </sheetData>
+  <autoFilter ref="B5:F5" xr:uid="{21A502A3-9C52-4270-99C9-763E766B38B8}"/>
+  <mergeCells count="1">
+    <mergeCell ref="C4:F4"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B6:F45">
+    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;12Inputs&amp;L&amp;G</oddHeader>
+    <oddFooter>&amp;L&amp;F&amp;C&amp;D  ·  v1.2  ·  As of 05/29/2026&amp;R&amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52888DDD-2087-4FEA-943B-79F183927A39}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:F25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5.77734375" customWidth="1"/>
+    <col min="2" max="2" width="30.77734375" customWidth="1"/>
+    <col min="3" max="10" width="15.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+    </row>
+    <row r="5" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="27">
         <f>Inputs!C6</f>
         <v>10000000</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="27">
         <f>Inputs!D6</f>
         <v>10500000</v>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="27">
         <f>Inputs!E6</f>
         <v>11025000</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="27">
         <f>Inputs!F6</f>
         <v>11576250</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B7" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" s="22">
+    <row r="7" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="27">
         <f>Inputs!C8</f>
         <v>6000000</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="27">
         <f>Inputs!D8</f>
         <v>6300000</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="27">
         <f>Inputs!E8</f>
         <v>6615000</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="27">
         <f>Inputs!F8</f>
         <v>6945750</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B8" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="23">
+    <row r="8" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="28">
         <f>C6-C7</f>
         <v>4000000</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="28">
         <f>D6-D7</f>
         <v>4200000</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="28">
         <f>E6-E7</f>
         <v>4410000</v>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="28">
         <f>F6-F7</f>
         <v>4630500</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B9" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9" s="24">
+    <row r="9" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="29">
         <f>IFERROR(C8/C6,0)</f>
         <v>0.4</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="29">
         <f>IFERROR(D8/D6,0)</f>
         <v>0.4</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="29">
         <f>IFERROR(E8/E6,0)</f>
         <v>0.4</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="29">
         <f>IFERROR(F8/F6,0)</f>
         <v>0.4</v>
       </c>
     </row>
+    <row r="10" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="18" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="19" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="23" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C4:F4"/>
+  </mergeCells>
   <conditionalFormatting sqref="C9:F9">
     <cfRule type="iconSet" priority="1">
       <iconSet iconSet="3Arrows">
@@ -1373,22 +1785,27 @@
       </iconSet>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B6:F45">
+    <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;12Calculations</oddHeader>
-    <oddFooter>&amp;R&amp;P of &amp;N&amp;L&amp;F</oddFooter>
+    <oddFooter>&amp;L&amp;F&amp;C&amp;D  ·  v1.2  ·  As of 05/29/2026&amp;R&amp;P of &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B347AA80-095D-45D2-BB58-6BC6424EF2F5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{809F5794-4E7A-4727-94E7-7F6FC89D264E}">
   <sheetPr>
     <tabColor rgb="FF005E34"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:F10"/>
+  <dimension ref="B2:G15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.77734375" customWidth="1"/>
@@ -1396,116 +1813,164 @@
     <col min="3" max="10" width="15.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:7" ht="18" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B6" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="22">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="30">
+        <f>Calc!F6</f>
+        <v>11576250</v>
+      </c>
+      <c r="E4" s="30">
+        <f>Calc!F8</f>
+        <v>4630500</v>
+      </c>
+      <c r="G4" s="32">
+        <f>Calc!F9</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C5" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="E5" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="G5" s="31" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="7.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C7" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+    </row>
+    <row r="8" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" s="24" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B9" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="27">
         <f>Calc!C6</f>
         <v>10000000</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D9" s="27">
         <f>Calc!D6</f>
         <v>10500000</v>
       </c>
-      <c r="E6" s="22">
+      <c r="E9" s="27">
         <f>Calc!E6</f>
         <v>11025000</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F9" s="27">
         <f>Calc!F6</f>
         <v>11576250</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B7" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" s="22">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B10" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10" s="27">
         <f>Calc!C8</f>
         <v>4000000</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D10" s="27">
         <f>Calc!D8</f>
         <v>4200000</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E10" s="27">
         <f>Calc!E8</f>
         <v>4410000</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F10" s="27">
         <f>Calc!F8</f>
         <v>4630500</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B8" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="25">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B11" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" s="33">
         <f>Calc!C9</f>
         <v>0.4</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D11" s="33">
         <f>Calc!D9</f>
         <v>0.4</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E11" s="33">
         <f>Calc!E9</f>
         <v>0.4</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F11" s="33">
         <f>Calc!F9</f>
         <v>0.4</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B10" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="C10" s="27">
-        <f>SUM(C6:F6)</f>
+    <row r="12" spans="2:7" ht="7.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B13" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" s="35">
+        <f>SUM(C9:F9)</f>
         <v>43101250</v>
       </c>
     </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B15" s="20" t="s">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C7:F7"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B9:F11">
+    <cfRule type="expression" dxfId="1" priority="1" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;12Output Summary</oddHeader>
-    <oddFooter>&amp;R&amp;P of &amp;N&amp;L&amp;F</oddFooter>
+    <oddFooter>&amp;L&amp;F&amp;C&amp;D  ·  v1.2  ·  As of 05/29/2026&amp;R&amp;P of &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{497841F3-0E79-4946-8276-4E956244ABE5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A54EFFA5-7080-4D20-A5E3-86D0AA1E9046}">
   <sheetPr>
     <tabColor rgb="FFA5A5A5"/>
   </sheetPr>
-  <dimension ref="B2:C9"/>
+  <dimension ref="B2:C12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.77734375" customWidth="1"/>
@@ -1516,55 +1981,84 @@
   <sheetData>
     <row r="2" spans="2:3" ht="18" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B5" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>59</v>
+      <c r="B5" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B6" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" s="28">
+      <c r="B6" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" s="36">
         <v>0.1</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B7" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" s="28">
+      <c r="B7" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" s="36">
         <v>0.21</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B8" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="5">
+      <c r="B8" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" s="36">
+        <v>8.5000000000000006E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B9" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" s="36">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B10" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B9" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="5">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B11" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B12" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C12" s="5">
         <v>252</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B6:C30">
+    <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;12Reference</oddHeader>
-    <oddFooter>&amp;R&amp;P of &amp;N&amp;L&amp;F</oddFooter>
+    <oddFooter>&amp;L&amp;F&amp;C&amp;D  ·  v1.2  ·  As of 05/29/2026&amp;R&amp;P of &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>